--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>ashok kumar bomjon</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851177886</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851177886</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9851177886</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9851177886</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.72007</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.72007</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +942,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.3763</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.3763</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : no signal showing   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1015,7 +1005,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1306,7 +1296,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : no signal showing   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -483,13 +483,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -501,17 +501,17 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -524,12 +524,12 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -982,6 +982,209 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377973</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Bibek ghemasu</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Bibek ghemasu</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9861518467</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34:13 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>BKT9861518467</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52:34 AM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34:13 PM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinyak , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>9861518467@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>02:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -996,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1005,7 +1208,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1033,7 +1236,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1043,7 +1246,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1078,7 +1281,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 11m</t>
+          <t>23h 56m</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1318,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1130,203 +1333,311 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1377808</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>ashok kumar bomjon</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : no signal showing   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>25 Oct 2026 10:04:29 AM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>23h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1377973</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Bibek ghemasu</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34:13 PM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52:34 AM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34:13 PM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1d 41m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,12 +494,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1052,10 +1052,8 @@
           <t>Bibek ghemasu</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9861518467</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9861518467</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1145,10 +1143,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1159,32 +1155,454 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377918</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9851160975</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9851160975</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:13:48 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.68498</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>near Holy Vision Technical Campus, M8MM+WV7, Sankhamul Marg, Kathmandu 44600, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>ideahub@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>02:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB154</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.33462</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 41m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 45m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>iptv isuue</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378266</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sunrise sound service Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sunrise sound service Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9851005949</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851005949</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:00:32 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.74037</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Vidhyalaya (???????? ????????) - School Budhanilkantha 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>rajzcrestha99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>02:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L2-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.36019</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>19h 55m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1199,11 +1617,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1236,7 +1654,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1664,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1281,7 +1699,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 56m</t>
+          <t>23h 23m</t>
         </is>
       </c>
     </row>
@@ -1322,10 +1740,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1340,10 +1758,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1398,10 +1816,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -1417,7 +1835,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1432,212 +1850,369 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1377808</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>ashok kumar bomjon</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Blank TV Display</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : no signal showing   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>25 Oct 2026 10:04:29 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>23h 11m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>TKT1377808</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>ashok kumar bomjon</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : no signal showing   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 09:15:39 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 10:04:29 AM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 09:15:39 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>TKT1377973</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Bibek ghemasu</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>25 Oct 2026 11:52:34 AM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>1d 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1377918</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:13:48 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378266</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Sunrise sound service Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:00:32 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>19h 55m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1251,10 +1251,8 @@
           <t>Idea Hub</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9851160975</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9851160975</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1289,10 +1287,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.68498</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.68498</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1348,25 +1344,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB154</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33462</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33462</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1462,10 +1454,8 @@
           <t>Sunrise sound service Pvt Ltd</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9851005949</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9851005949</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1500,10 +1490,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.74037</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.74037</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1559,25 +1547,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L2-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.36019</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.36019</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1626,7 +1610,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2115,7 +2099,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2182,7 +2166,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1587,6 +1587,205 @@
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 2:38 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371692</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Pralad Upreti</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Pralad Upreti</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9855089977</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 02:38:42 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9846588576</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 12:34:10 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 02:38:42 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>near by Universal Dental Hospital - Dental hygienist - Kathmandu Metropolitan, Kathmandu, Bagmati, N</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>20:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>11d 2h 4m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1610,7 +1809,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1638,7 +1837,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1648,7 +1847,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1683,7 +1882,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 23m</t>
+          <t>2d 23h 55m</t>
         </is>
       </c>
     </row>
@@ -1724,10 +1923,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1800,10 +1999,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -2197,6 +2396,73 @@
       <c r="M24" s="3" t="inlineStr">
         <is>
           <t>19h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1371692</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Pralad Upreti</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 02:38:42 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 12:34:10 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 02:38:42 PM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>11d 2h 4m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1657,10 +1657,8 @@
           <t>Pralad Upreti</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9855089977</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9855089977</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1746,10 +1744,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -1760,7 +1756,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1809,7 +1805,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2432,7 +2428,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="20" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1780,6 +1780,213 @@
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 3:54 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378099</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9861778881</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:16:55 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9861778881K</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:16:55 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:54:01 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.65445</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Sitapakha, Imadol, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>crackmaharjan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.3385</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1833,7 +2040,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1854,7 +2061,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1919,14 +2126,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1995,14 +2202,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1842,20 +1842,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Krasan Maharjan</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9861778881</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9861778881</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1890,10 +1884,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.65445</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.65445</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1945,25 +1937,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.3385</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.3385</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,12 +529,12 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,631 @@
         </is>
       </c>
       <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 4:59 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>STB return</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373194</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Lamichhane</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Lamichhane</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851239211</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851239211</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 07:29:56 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.71923</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Jorpati near New Generation Driving School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>saugatlamichanne165@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>05:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L61-4</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.37675</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>9d 21h 29m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:05 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378747</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Ekata Interprises</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Ekata Interprises</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9849875913</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9849875913</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 09:16:00 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>haribot chowk hattiban, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>digambar.das27@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>07:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L7-2</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>7h 49m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378099</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9861778881</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:33:38 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9861778881K</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:16:55 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:33:38 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.65445</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Sitapakha, Imadol, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>crackmaharjan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>06:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.3385</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1991,7 +2616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2000,7 +2625,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2028,7 +2653,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2038,7 +2663,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2049,7 +2674,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2698,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 55m</t>
+          <t>3d 6h 54m</t>
         </is>
       </c>
     </row>
@@ -2110,106 +2735,101 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -2227,254 +2847,166 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1377808</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>ashok kumar bomjon</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Blank TV Display</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : no signal showing   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>25 Oct 2026 10:04:29 AM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>23h 11m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1377973</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Bibek ghemasu</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 12:34:13 PM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>25 Oct 2026 11:52:34 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 12:34:13 PM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 41m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1377918</t>
+          <t>TKT1377808</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Idea Hub</t>
+          <t>ashok kumar bomjon</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2494,22 +3026,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : no signal showing   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:58:54 PM</t>
+          <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>25 Oct 2026 11:13:48 AM</t>
+          <t>25 Oct 2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:58:54 PM</t>
+          <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2519,29 +3051,29 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 45m</t>
+          <t>23h 11m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1378266</t>
+          <t>TKT1377973</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Sunrise sound service Pvt Ltd</t>
+          <t>Bibek ghemasu</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2561,22 +3093,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:55:34 PM</t>
+          <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>25 Oct 2026 05:00:32 PM</t>
+          <t>25 Oct 2026 11:52:34 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:55:34 PM</t>
+          <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2586,74 +3118,409 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>19h 55m</t>
+          <t>1d 41m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>TKT1377918</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:13:48 AM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378266</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Sunrise sound service Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:00:32 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>19h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>TKT1371692</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Pralad Upreti</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>26 Oct 2026 02:38:42 PM</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>15 Oct 2026 12:34:10 PM</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>26 Oct 2026 02:38:42 PM</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>11d 2h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373194</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Lamichhane</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 07:29:56 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>9d 21h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1378747</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Ekata Interprises</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 09:16:00 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>7h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378099</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:33:38 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:16:55 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:33:38 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2037,20 +2037,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Saugat Lamichhane</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851239211</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851239211</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2085,10 +2079,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.71923</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.71923</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2144,25 +2136,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L61-4</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.37675</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.37675</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2258,10 +2246,8 @@
           <t>Ekata Interprises</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9849875913</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9849875913</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2351,10 +2337,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2365,7 +2349,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2451,20 +2435,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Krasan Maharjan</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9861778881</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9861778881</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2499,10 +2477,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.65445</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.65445</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2558,50 +2534,456 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.3385</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.3385</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 16m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:12 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379083</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Dulal</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Dulal</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9849715976</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:18:42 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9849715976</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:18:42 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:12:58 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.65241</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Imadol Ochu Height surayada school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>frankwankey@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L33-8</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.34204</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378866</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:14:05 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:12:24 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:10:59 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.66608</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near to Boje Pokhari - Pond Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.35222</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>6h 56m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2625,7 +3007,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2653,7 +3035,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2674,7 +3056,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -2757,390 +3139,297 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Device Recovery</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Setup Box Recovery</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1377808</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>ashok kumar bomjon</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Blank TV Display</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : no signal showing   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>25 Oct 2026 10:04:29 AM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>23h 11m</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1377973</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Bibek ghemasu</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 12:34:13 PM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>25 Oct 2026 11:52:34 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 12:34:13 PM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 41m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1377918</t>
+          <t>TKT1377808</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Idea Hub</t>
+          <t>ashok kumar bomjon</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3160,22 +3449,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : no signal showing   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:58:54 PM</t>
+          <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>25 Oct 2026 11:13:48 AM</t>
+          <t>25 Oct 2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:58:54 PM</t>
+          <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -3185,29 +3474,29 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 45m</t>
+          <t>23h 11m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1378266</t>
+          <t>TKT1377973</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sunrise sound service Pvt Ltd</t>
+          <t>Bibek ghemasu</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3227,22 +3516,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:55:34 PM</t>
+          <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>25 Oct 2026 05:00:32 PM</t>
+          <t>25 Oct 2026 11:52:34 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:55:34 PM</t>
+          <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3252,19 +3541,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>19h 55m</t>
+          <t>1d 41m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1371692</t>
+          <t>TKT1377918</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Pralad Upreti</t>
+          <t>Idea Hub</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3294,22 +3583,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 02:38:42 PM</t>
+          <t>26 Oct 2026 12:58:54 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 12:34:10 PM</t>
+          <t>25 Oct 2026 11:13:48 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 02:38:42 PM</t>
+          <t>26 Oct 2026 12:58:54 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3319,29 +3608,29 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>11d 2h 4m</t>
+          <t>1d 1h 45m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1373194</t>
+          <t>TKT1378266</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Saugat Lamichhane</t>
+          <t>Sunrise sound service Pvt Ltd</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Device Recovery</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3356,27 +3645,27 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:59:10 PM</t>
+          <t>26 Oct 2026 12:55:34 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 07:29:56 PM</t>
+          <t>25 Oct 2026 05:00:32 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:59:10 PM</t>
+          <t>26 Oct 2026 12:55:34 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3386,19 +3675,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>9d 21h 29m</t>
+          <t>19h 55m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1378747</t>
+          <t>TKT1371692</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Ekata Interprises</t>
+          <t>Pralad Upreti</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3423,27 +3712,27 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 05:05:07 PM</t>
+          <t>26 Oct 2026 02:38:42 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 09:16:00 AM</t>
+          <t>15 Oct 2026 12:34:10 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 05:05:07 PM</t>
+          <t>26 Oct 2026 02:38:42 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3453,72 +3742,206 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>7h 49m</t>
+          <t>11d 2h 4m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>TKT1373194</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Lamichhane</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 07:29:56 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>9d 21h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1378747</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Ekata Interprises</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 09:16:00 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>7h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>TKT1378099</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Krasan Maharjan</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 04:33:38 PM</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>25 Oct 2026 02:16:55 PM</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 04:33:38 PM</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>1d 2h 16m</t>
         </is>

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -2644,10 +2644,8 @@
           <t>Sujan Dulal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9849715976</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9849715976</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2682,10 +2680,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.65241</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.65241</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2737,25 +2733,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L33-8</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.34204</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.34204</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2851,10 +2843,8 @@
           <t>Padam Nepali</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9860495460</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9860495460</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2889,10 +2879,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.66608</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.66608</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2940,48 +2928,247 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.35222</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.35222</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>6h 56m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>6h 56m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>6h 58m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:35 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378708</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Raju subedi</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Raju subedi</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9843663665</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:35:32 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>KLK9843663665</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 08:38:49 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:35:32 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Tahachal near, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>9843663665@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>07:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>8h 56m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -2998,16 +3185,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3035,7 +3222,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -3045,7 +3232,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3056,7 +3243,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3267,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 6h 54m</t>
+          <t>2d 23h 7m</t>
         </is>
       </c>
     </row>
@@ -3157,14 +3344,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3275,41 +3462,41 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3508,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -3336,167 +3523,123 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1377808</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>ashok kumar bomjon</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Blank TV Display</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : no signal showing   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>25 Oct 2026 10:04:29 AM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 09:15:39 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>23h 11m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1377973</t>
+          <t>TKT1377808</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bibek ghemasu</t>
+          <t>ashok kumar bomjon</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3516,22 +3659,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : no signal showing   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:34:13 PM</t>
+          <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>25 Oct 2026 11:52:34 AM</t>
+          <t>25 Oct 2026 10:04:29 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:34:13 PM</t>
+          <t>26 Oct 2026 09:15:39 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3541,19 +3684,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1d 41m</t>
+          <t>23h 11m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1377918</t>
+          <t>TKT1377973</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Idea Hub</t>
+          <t>Bibek ghemasu</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3583,22 +3726,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:58:54 PM</t>
+          <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>25 Oct 2026 11:13:48 AM</t>
+          <t>25 Oct 2026 11:52:34 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:58:54 PM</t>
+          <t>26 Oct 2026 12:34:13 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3608,29 +3751,29 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 45m</t>
+          <t>1d 41m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1378266</t>
+          <t>TKT1377918</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sunrise sound service Pvt Ltd</t>
+          <t>Idea Hub</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3650,22 +3793,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:55:34 PM</t>
+          <t>26 Oct 2026 12:58:54 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>25 Oct 2026 05:00:32 PM</t>
+          <t>25 Oct 2026 11:13:48 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 12:55:34 PM</t>
+          <t>26 Oct 2026 12:58:54 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3675,29 +3818,29 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>19h 55m</t>
+          <t>1d 1h 45m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1371692</t>
+          <t>TKT1378266</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Pralad Upreti</t>
+          <t>Sunrise sound service Pvt Ltd</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3717,22 +3860,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 02:38:42 PM</t>
+          <t>26 Oct 2026 12:55:34 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>15 Oct 2026 12:34:10 PM</t>
+          <t>25 Oct 2026 05:00:32 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 02:38:42 PM</t>
+          <t>26 Oct 2026 12:55:34 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3742,29 +3885,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>11d 2h 4m</t>
+          <t>19h 55m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1373194</t>
+          <t>TKT1371692</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Saugat Lamichhane</t>
+          <t>Pralad Upreti</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Device Recovery</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3784,22 +3927,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:59:10 PM</t>
+          <t>26 Oct 2026 02:38:42 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026 07:29:56 PM</t>
+          <t>15 Oct 2026 12:34:10 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 04:59:10 PM</t>
+          <t>26 Oct 2026 02:38:42 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3809,29 +3952,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>9d 21h 29m</t>
+          <t>11d 2h 4m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1378747</t>
+          <t>TKT1373194</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Ekata Interprises</t>
+          <t>Saugat Lamichhane</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3851,22 +3994,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 05:05:07 PM</t>
+          <t>26 Oct 2026 04:59:10 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 09:16:00 AM</t>
+          <t>16 Oct 2026 07:29:56 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 05:05:07 PM</t>
+          <t>26 Oct 2026 04:59:10 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -3876,74 +4019,208 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>7h 49m</t>
+          <t>9d 21h 29m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>TKT1378747</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Ekata Interprises</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 09:16:00 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>7h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>TKT1378099</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Krasan Maharjan</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>26 Oct 2026 04:33:38 PM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>25 Oct 2026 02:16:55 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>26 Oct 2026 04:33:38 PM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>1d 2h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378708</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Raju subedi</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:35:32 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 08:38:49 AM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:35:32 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>8h 56m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_26_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_26_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3038,10 +3038,8 @@
           <t>Raju subedi</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9843663665</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9843663665</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3131,10 +3129,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3141,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3194,7 +3190,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4190,7 +4186,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
